--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty PSU Bond Plus SDL Sep 2027 4060 Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty PSU Bond Plus SDL Sep 2027 4060 Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="163">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty PSU Bond Plus SDL Sep 2027 40:60 Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -64,21 +64,21 @@
     <t>Government Securities</t>
   </si>
   <si>
+    <t>State Government of Tamil Nadu</t>
+  </si>
+  <si>
+    <t>IN3120170078</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
     <t>State Government of Rajasthan</t>
   </si>
   <si>
     <t>IN2920170072</t>
   </si>
   <si>
-    <t>SOV</t>
-  </si>
-  <si>
-    <t>State Government of Tamil Nadu</t>
-  </si>
-  <si>
-    <t>IN3120170078</t>
-  </si>
-  <si>
     <t>State Government of Maharashtra</t>
   </si>
   <si>
@@ -94,30 +94,30 @@
     <t>IN2120170047</t>
   </si>
   <si>
+    <t>IN2220170103</t>
+  </si>
+  <si>
+    <t>IN2220210230</t>
+  </si>
+  <si>
     <t>State Government of Uttar Pradesh</t>
   </si>
   <si>
     <t>IN3320170100</t>
   </si>
   <si>
-    <t>IN2220170103</t>
-  </si>
-  <si>
-    <t>IN2220210230</t>
-  </si>
-  <si>
     <t>IN3120170086</t>
   </si>
   <si>
+    <t>State Government of Gujarat</t>
+  </si>
+  <si>
+    <t>IN1520170086</t>
+  </si>
+  <si>
     <t>IN3320170092</t>
   </si>
   <si>
-    <t>State Government of Gujarat</t>
-  </si>
-  <si>
-    <t>IN1520170086</t>
-  </si>
-  <si>
     <t>State Government of Chhattisgarh</t>
   </si>
   <si>
@@ -133,18 +133,24 @@
     <t>IN1320210033</t>
   </si>
   <si>
+    <t>IN3320170050</t>
+  </si>
+  <si>
     <t>IN1520170078</t>
   </si>
   <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920170025</t>
+  </si>
+  <si>
     <t>State Government of Himachal pradesh</t>
   </si>
   <si>
     <t>IN1720170035</t>
   </si>
   <si>
-    <t>IN3320170050</t>
-  </si>
-  <si>
     <t>IN1320210025</t>
   </si>
   <si>
@@ -154,9 +160,6 @@
     <t>IN1620170036</t>
   </si>
   <si>
-    <t>State Government of Karnataka</t>
-  </si>
-  <si>
     <t>IN1920200087</t>
   </si>
   <si>
@@ -166,12 +169,15 @@
     <t>IN1820170075</t>
   </si>
   <si>
+    <t>State Government of Telangana</t>
+  </si>
+  <si>
+    <t>IN4520190088</t>
+  </si>
+  <si>
     <t>IN1520170094</t>
   </si>
   <si>
-    <t>State Government of Telangana</t>
-  </si>
-  <si>
     <t>IN4520190039</t>
   </si>
   <si>
@@ -181,9 +187,6 @@
     <t>IN1220170048</t>
   </si>
   <si>
-    <t>IN2120170013</t>
-  </si>
-  <si>
     <t>IN1520210098</t>
   </si>
   <si>
@@ -199,15 +202,15 @@
     <t>IN3120170060</t>
   </si>
   <si>
-    <t>IN4520190088</t>
-  </si>
-  <si>
-    <t>IN2120170039</t>
+    <t>IN1520230062</t>
   </si>
   <si>
     <t>IN3520190023</t>
   </si>
   <si>
+    <t>IN2120170021</t>
+  </si>
+  <si>
     <t>IN1620220096</t>
   </si>
   <si>
@@ -217,27 +220,18 @@
     <t>IN3320170068</t>
   </si>
   <si>
-    <t>IN1920170025</t>
-  </si>
-  <si>
     <t>State Government of West Bengal</t>
   </si>
   <si>
     <t>IN3420170018</t>
   </si>
   <si>
-    <t>IN2120170021</t>
-  </si>
-  <si>
     <t>State Government of Kerala</t>
   </si>
   <si>
     <t>IN2020170063</t>
   </si>
   <si>
-    <t>IN4520190070</t>
-  </si>
-  <si>
     <t>IN3120170045</t>
   </si>
   <si>
@@ -259,12 +253,18 @@
     <t>IN1520170060</t>
   </si>
   <si>
+    <t>IN1620170028</t>
+  </si>
+  <si>
     <t>State Government of Andhra Pradesh</t>
   </si>
   <si>
     <t>IN1020170040</t>
   </si>
   <si>
+    <t>IN4520190096</t>
+  </si>
+  <si>
     <t>IN3320170084</t>
   </si>
   <si>
@@ -283,12 +283,12 @@
     <t>IN1020180098</t>
   </si>
   <si>
+    <t>IN4520190104</t>
+  </si>
+  <si>
     <t>IN1320160170</t>
   </si>
   <si>
-    <t>IN4520190096</t>
-  </si>
-  <si>
     <t>IN2920160420</t>
   </si>
   <si>
@@ -316,6 +316,15 @@
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
+    <t>NABARD</t>
+  </si>
+  <si>
+    <t>INE261F08EI9</t>
+  </si>
+  <si>
+    <t>ICRA AAA</t>
+  </si>
+  <si>
     <t>Indian Railway Finance Corporation Ltd. **</t>
   </si>
   <si>
@@ -325,39 +334,30 @@
     <t>CRISIL AAA</t>
   </si>
   <si>
-    <t>NABARD</t>
-  </si>
-  <si>
-    <t>INE261F08EI9</t>
-  </si>
-  <si>
-    <t>ICRA AAA</t>
+    <t>Power Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE134E08IX1</t>
+  </si>
+  <si>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F08CF9</t>
+  </si>
+  <si>
+    <t>INE134E08JC3</t>
   </si>
   <si>
     <t>INE261F08EF5</t>
   </si>
   <si>
-    <t>Power Finance Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE134E08IX1</t>
-  </si>
-  <si>
-    <t>NABARD **</t>
-  </si>
-  <si>
-    <t>INE261F08CF9</t>
-  </si>
-  <si>
     <t>Power Grid Corporation Of India Ltd. **</t>
   </si>
   <si>
     <t>INE752E07OG5</t>
   </si>
   <si>
-    <t>INE134E08JC3</t>
-  </si>
-  <si>
     <t>Export-Import Bank Of India **</t>
   </si>
   <si>
@@ -367,9 +367,6 @@
     <t>INE134E08LH8</t>
   </si>
   <si>
-    <t>Indian Railway Finance Corporation Ltd.</t>
-  </si>
-  <si>
     <t>INE053F07AB5</t>
   </si>
   <si>
@@ -400,7 +397,13 @@
     <t>INE053F09EO6</t>
   </si>
   <si>
-    <t>INE134E08IO0</t>
+    <t>INE752E07JN1</t>
+  </si>
+  <si>
+    <t>INE752E07KA6</t>
+  </si>
+  <si>
+    <t>INE752E07OE0</t>
   </si>
   <si>
     <t>Rural Electrification Corporation Ltd. **</t>
@@ -415,9 +418,6 @@
     <t>INE752E07IX2</t>
   </si>
   <si>
-    <t>INE752E07KA6</t>
-  </si>
-  <si>
     <t>INE752E07MT2</t>
   </si>
   <si>
@@ -487,19 +487,22 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
   </si>
   <si>
+    <t>Debt Index Replication Factor (DIRF) as on 31-5-2025</t>
+  </si>
+  <si>
+    <t>As per SEBI circular no. SEBI/HO/IMD/PoD/P/CIR/2024/183 dated December 31,2024, with respect to introduction of mutual Funds Lite (MF Lite) framework for passively managed schemes of Mutual Funds, Debt Index Replication Factor (DIRF) is disclosed for debt oriented passive schemes.</t>
+  </si>
+  <si>
     <t>Scheme Riskometer</t>
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty PSU Bond Plus SDL Sep 2027 40:60 Index</t>
   </si>
 </sst>
 </file>
@@ -511,7 +514,7 @@
     <numFmt numFmtId="178" formatCode="##0.00%"/>
     <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -519,13 +522,21 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.5"/>
-      <name val="Verdana"/>
+      <sz val="8.25"/>
+      <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.25"/>
-      <name val="Microsoft Sans Serif"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
@@ -699,37 +710,63 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
       <protection/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -740,51 +777,43 @@
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
       <protection/>
     </xf>
   </cellXfs>
@@ -873,13 +902,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>155</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -897,8 +926,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="27508200"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="28279725"/>
+          <a:ext cx="3752850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -912,13 +941,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>157</xdr:row>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>167</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -936,8 +965,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30365700"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="31137225"/>
+          <a:ext cx="3752850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1270,11 +1299,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J156"/>
+  <dimension ref="B1:J158"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="53.57142857142857" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="56.285714285714285" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="16.714285714285715" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="19.714285714285715" collapsed="true"/>
@@ -1370,10 +1399,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>848081.9999999999</v>
+        <v>898861.4599999998</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9642237819438998</v>
+        <v>0.9655726926536997</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1407,10 +1436,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>848081.9999999999</v>
+        <v>898861.4599999998</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9642237819438998</v>
+        <v>0.9655726926536997</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1444,10 +1473,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>512794.47000000015</v>
+        <v>542373.2299999999</v>
       </c>
       <c r="H9" s="10">
-        <v>0.5830198297134999</v>
+        <v>0.5826268044844997</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1464,22 +1493,22 @@
         <v>17</v>
       </c>
       <c r="D10" s="14">
-        <v>7.45</v>
+        <v>7.18</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="15">
-        <v>70178500</v>
+        <v>70803000</v>
       </c>
       <c r="G10" s="16">
-        <v>71070.54</v>
+        <v>72545.04</v>
       </c>
       <c r="H10" s="17">
-        <v>0.08080339503</v>
+        <v>0.0779291500736</v>
       </c>
       <c r="I10" s="16">
-        <v>7.03</v>
+        <v>6.03</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1493,22 +1522,22 @@
         <v>20</v>
       </c>
       <c r="D11" s="14">
-        <v>7.18</v>
+        <v>7.45</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="15">
-        <v>68303000</v>
+        <v>70178500</v>
       </c>
       <c r="G11" s="16">
-        <v>68809.19</v>
+        <v>72398.88</v>
       </c>
       <c r="H11" s="17">
-        <v>0.0782323612747</v>
+        <v>0.0777721424467</v>
       </c>
       <c r="I11" s="16">
-        <v>6.97</v>
+        <v>6.05</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1528,16 +1557,16 @@
         <v>18</v>
       </c>
       <c r="F12" s="15">
-        <v>52019130</v>
+        <v>59519130</v>
       </c>
       <c r="G12" s="16">
-        <v>52429.82</v>
+        <v>61030.02</v>
       </c>
       <c r="H12" s="17">
-        <v>0.0596098954196</v>
+        <v>0.0655595143042</v>
       </c>
       <c r="I12" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1545,7 +1574,7 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>23</v>
@@ -1557,16 +1586,16 @@
         <v>18</v>
       </c>
       <c r="F13" s="15">
-        <v>24495000</v>
+        <v>26495000</v>
       </c>
       <c r="G13" s="16">
-        <v>25484.79</v>
+        <v>27955.27</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0289748403998</v>
+        <v>0.0300300396992</v>
       </c>
       <c r="I13" s="16">
-        <v>6.99</v>
+        <v>6.04</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1586,16 +1615,16 @@
         <v>18</v>
       </c>
       <c r="F14" s="15">
-        <v>19783000</v>
+        <v>18783000</v>
       </c>
       <c r="G14" s="16">
-        <v>20058.93</v>
+        <v>19384.36</v>
       </c>
       <c r="H14" s="17">
-        <v>0.022805928373</v>
+        <v>0.0208230183555</v>
       </c>
       <c r="I14" s="16">
-        <v>6.99</v>
+        <v>6.05</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1603,28 +1632,28 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>27</v>
-      </c>
       <c r="D15" s="14">
-        <v>7.47</v>
+        <v>7.33</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="15">
-        <v>16943600</v>
+        <v>17667000</v>
       </c>
       <c r="G15" s="16">
-        <v>17177.18</v>
+        <v>18181.9</v>
       </c>
       <c r="H15" s="17">
-        <v>0.0195295330673</v>
+        <v>0.0195313148042</v>
       </c>
       <c r="I15" s="16">
-        <v>7.01</v>
+        <v>6.03</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1635,25 +1664,25 @@
         <v>21</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="14">
-        <v>7.33</v>
+        <v>6.38</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="15">
-        <v>16667000</v>
+        <v>17500000</v>
       </c>
       <c r="G16" s="16">
-        <v>16852.80</v>
+        <v>17662.28</v>
       </c>
       <c r="H16" s="17">
-        <v>0.0191607303921</v>
+        <v>0.0189731299171</v>
       </c>
       <c r="I16" s="16">
-        <v>6.97</v>
+        <v>6.01</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1661,28 +1690,28 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="14">
-        <v>6.38</v>
+        <v>7.47</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="15">
-        <v>16500000</v>
+        <v>16943600</v>
       </c>
       <c r="G17" s="16">
-        <v>16323.91</v>
+        <v>17488.68</v>
       </c>
       <c r="H17" s="17">
-        <v>0.0185594108074</v>
+        <v>0.0187866457625</v>
       </c>
       <c r="I17" s="16">
-        <v>6.95</v>
+        <v>6.05</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1690,7 +1719,7 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>30</v>
@@ -1702,16 +1731,16 @@
         <v>18</v>
       </c>
       <c r="F18" s="15">
-        <v>15210800</v>
+        <v>16710800</v>
       </c>
       <c r="G18" s="16">
-        <v>15331.82</v>
+        <v>17138.40</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0174314576474</v>
+        <v>0.0184103688635</v>
       </c>
       <c r="I18" s="16">
-        <v>6.98</v>
+        <v>6.03</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1719,28 +1748,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="14">
-        <v>7.37</v>
+        <v>7.21</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="15">
-        <v>13188700</v>
+        <v>13500000</v>
       </c>
       <c r="G19" s="16">
-        <v>13337.28</v>
+        <v>13845.44</v>
       </c>
       <c r="H19" s="17">
-        <v>0.0151637725626</v>
+        <v>0.0148730136697</v>
       </c>
       <c r="I19" s="16">
-        <v>7.01</v>
+        <v>6.03</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -1748,28 +1777,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="14">
-        <v>7.21</v>
+        <v>7.37</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="15">
-        <v>13000000</v>
+        <v>13188700</v>
       </c>
       <c r="G20" s="16">
-        <v>13104.25</v>
+        <v>13578.44</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0148988299416</v>
+        <v>0.0145861976025</v>
       </c>
       <c r="I20" s="16">
-        <v>6.97</v>
+        <v>6.05</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -1792,13 +1821,13 @@
         <v>11567300</v>
       </c>
       <c r="G21" s="16">
-        <v>11721.89</v>
+        <v>11936.02</v>
       </c>
       <c r="H21" s="17">
-        <v>0.0133271607077</v>
+        <v>0.0128218813286</v>
       </c>
       <c r="I21" s="16">
-        <v>7.02</v>
+        <v>6.06</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -1821,13 +1850,13 @@
         <v>10590100</v>
       </c>
       <c r="G22" s="16">
-        <v>10490.22</v>
+        <v>10698.34</v>
       </c>
       <c r="H22" s="17">
-        <v>0.0119268179278</v>
+        <v>0.0114923438376</v>
       </c>
       <c r="I22" s="16">
-        <v>6.95</v>
+        <v>6.01</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -1850,13 +1879,13 @@
         <v>9500000</v>
       </c>
       <c r="G23" s="16">
-        <v>9474.90</v>
+        <v>9651.90</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0107724535028</v>
+        <v>0.0103682396976</v>
       </c>
       <c r="I23" s="16">
-        <v>6.98</v>
+        <v>6.01</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -1864,28 +1893,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>39</v>
       </c>
       <c r="D24" s="14">
-        <v>7.17</v>
+        <v>7.29</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="15">
-        <v>8304640</v>
+        <v>9000000</v>
       </c>
       <c r="G24" s="16">
-        <v>8362.96</v>
+        <v>9233.59</v>
       </c>
       <c r="H24" s="17">
-        <v>0.009508237316</v>
+        <v>0.0099188837834</v>
       </c>
       <c r="I24" s="16">
-        <v>6.97</v>
+        <v>6.05</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
@@ -1893,28 +1922,28 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>41</v>
-      </c>
       <c r="D25" s="14">
-        <v>7.30</v>
+        <v>7.17</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="15">
-        <v>7500000</v>
+        <v>8304640</v>
       </c>
       <c r="G25" s="16">
-        <v>7569.25</v>
+        <v>8507.31</v>
       </c>
       <c r="H25" s="17">
-        <v>0.0086058315841</v>
+        <v>0.0091387011119</v>
       </c>
       <c r="I25" s="16">
-        <v>7.02</v>
+        <v>6.03</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
@@ -1922,28 +1951,28 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>42</v>
       </c>
       <c r="D26" s="14">
-        <v>7.29</v>
+        <v>7.38</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="15">
-        <v>7000000</v>
+        <v>7500000</v>
       </c>
       <c r="G26" s="16">
-        <v>7062.08</v>
+        <v>7730.16</v>
       </c>
       <c r="H26" s="17">
-        <v>0.0080292064753</v>
+        <v>0.0083038729971</v>
       </c>
       <c r="I26" s="16">
-        <v>7.01</v>
+        <v>6.03</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
@@ -1951,28 +1980,28 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D27" s="14">
-        <v>6.45</v>
+        <v>7.30</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="15">
-        <v>7000000</v>
+        <v>7500000</v>
       </c>
       <c r="G27" s="16">
-        <v>6939.71</v>
+        <v>7699.79</v>
       </c>
       <c r="H27" s="17">
-        <v>0.0078900783436</v>
+        <v>0.0082712490122</v>
       </c>
       <c r="I27" s="16">
-        <v>6.97</v>
+        <v>6.09</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
@@ -1980,28 +2009,28 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D28" s="14">
-        <v>7.29</v>
+        <v>6.45</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="15">
-        <v>6255000</v>
+        <v>7000000</v>
       </c>
       <c r="G28" s="16">
-        <v>6314.55</v>
+        <v>7067.66</v>
       </c>
       <c r="H28" s="17">
-        <v>0.0071793049284</v>
+        <v>0.0075922039164</v>
       </c>
       <c r="I28" s="16">
-        <v>6.99</v>
+        <v>6.02</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>13</v>
@@ -2015,22 +2044,22 @@
         <v>47</v>
       </c>
       <c r="D29" s="14">
-        <v>6.12</v>
+        <v>7.29</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="15">
-        <v>5875000</v>
+        <v>6255000</v>
       </c>
       <c r="G29" s="16">
-        <v>5780.02</v>
+        <v>6425.35</v>
       </c>
       <c r="H29" s="17">
-        <v>0.0065715729659</v>
+        <v>0.0069022232867</v>
       </c>
       <c r="I29" s="16">
-        <v>6.96</v>
+        <v>6.05</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>13</v>
@@ -2038,28 +2067,28 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="D30" s="14">
-        <v>7.42</v>
+        <v>6.12</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="15">
-        <v>5500000</v>
+        <v>5875000</v>
       </c>
       <c r="G30" s="16">
-        <v>5570.26</v>
+        <v>5897.20</v>
       </c>
       <c r="H30" s="17">
-        <v>0.0063330870878</v>
+        <v>0.0063348753245</v>
       </c>
       <c r="I30" s="16">
-        <v>7</v>
+        <v>6.01</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>13</v>
@@ -2067,28 +2096,28 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>50</v>
       </c>
       <c r="D31" s="14">
-        <v>7.25</v>
+        <v>7.42</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="15">
-        <v>5044300</v>
+        <v>5500000</v>
       </c>
       <c r="G31" s="16">
-        <v>5089.79</v>
+        <v>5669.06</v>
       </c>
       <c r="H31" s="17">
-        <v>0.0057868184481</v>
+        <v>0.0060898033486</v>
       </c>
       <c r="I31" s="16">
-        <v>6.97</v>
+        <v>6.07</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>13</v>
@@ -2102,22 +2131,22 @@
         <v>52</v>
       </c>
       <c r="D32" s="14">
-        <v>7.61</v>
+        <v>7.03</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="15">
-        <v>5000000</v>
+        <v>5167000</v>
       </c>
       <c r="G32" s="16">
-        <v>5078.61</v>
+        <v>5279.13</v>
       </c>
       <c r="H32" s="17">
-        <v>0.0057741073873</v>
+        <v>0.0056709337265</v>
       </c>
       <c r="I32" s="16">
-        <v>6.99</v>
+        <v>6.06</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>13</v>
@@ -2125,28 +2154,28 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="D33" s="14">
-        <v>7.30</v>
+        <v>7.25</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="15">
-        <v>5000000</v>
+        <v>5044300</v>
       </c>
       <c r="G33" s="16">
-        <v>5044.83</v>
+        <v>5179.65</v>
       </c>
       <c r="H33" s="17">
-        <v>0.0057357013377</v>
+        <v>0.0055640705715</v>
       </c>
       <c r="I33" s="16">
-        <v>7.02</v>
+        <v>6.03</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>13</v>
@@ -2154,13 +2183,13 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D34" s="14">
-        <v>7.22</v>
+        <v>7.61</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>18</v>
@@ -2169,13 +2198,13 @@
         <v>5000000</v>
       </c>
       <c r="G34" s="16">
-        <v>5039.68</v>
+        <v>5153.05</v>
       </c>
       <c r="H34" s="17">
-        <v>0.0057298460637</v>
+        <v>0.0055354963866</v>
       </c>
       <c r="I34" s="16">
-        <v>6.99</v>
+        <v>6.07</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>13</v>
@@ -2183,13 +2212,13 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>56</v>
       </c>
       <c r="D35" s="14">
-        <v>6.28</v>
+        <v>7.30</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>18</v>
@@ -2198,13 +2227,13 @@
         <v>5000000</v>
       </c>
       <c r="G35" s="16">
-        <v>4934.09</v>
+        <v>5128.66</v>
       </c>
       <c r="H35" s="17">
-        <v>0.0056097958927</v>
+        <v>0.0055092962222</v>
       </c>
       <c r="I35" s="16">
-        <v>6.96</v>
+        <v>6.09</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -2212,28 +2241,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="D36" s="14">
-        <v>7.40</v>
+        <v>6.28</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="15">
-        <v>4532000</v>
+        <v>5000000</v>
       </c>
       <c r="G36" s="16">
-        <v>4587.28</v>
+        <v>5036.31</v>
       </c>
       <c r="H36" s="17">
-        <v>0.0052154915096</v>
+        <v>0.0054100922379</v>
       </c>
       <c r="I36" s="16">
-        <v>7</v>
+        <v>6.01</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
@@ -2241,28 +2270,28 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>59</v>
       </c>
       <c r="D37" s="14">
-        <v>7.29</v>
+        <v>7.40</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="15">
-        <v>4300000</v>
+        <v>4532000</v>
       </c>
       <c r="G37" s="16">
-        <v>4338.4</v>
+        <v>4671.48</v>
       </c>
       <c r="H37" s="17">
-        <v>0.004932528288</v>
+        <v>0.0050181854746</v>
       </c>
       <c r="I37" s="16">
-        <v>7</v>
+        <v>6.04</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -2270,28 +2299,28 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>60</v>
       </c>
       <c r="D38" s="14">
-        <v>7.27</v>
+        <v>7.29</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="15">
-        <v>4293280</v>
+        <v>4300000</v>
       </c>
       <c r="G38" s="16">
-        <v>4332.08</v>
+        <v>4405.62</v>
       </c>
       <c r="H38" s="17">
-        <v>0.0049253427867</v>
+        <v>0.0047325940153</v>
       </c>
       <c r="I38" s="16">
-        <v>6.98</v>
+        <v>6.10</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>13</v>
@@ -2299,28 +2328,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D39" s="14">
-        <v>7.03</v>
+        <v>7.27</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="15">
-        <v>4167000</v>
+        <v>4293280</v>
       </c>
       <c r="G39" s="16">
-        <v>4180.14</v>
+        <v>4404.76</v>
       </c>
       <c r="H39" s="17">
-        <v>0.0047525951498</v>
+        <v>0.0047316701883</v>
       </c>
       <c r="I39" s="16">
-        <v>7.01</v>
+        <v>6.03</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -2328,28 +2357,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D40" s="14">
-        <v>7.35</v>
+        <v>7.40</v>
       </c>
       <c r="E40" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="15">
-        <v>4000000</v>
+        <v>3500000</v>
       </c>
       <c r="G40" s="16">
-        <v>4044.76</v>
+        <v>3608.28</v>
       </c>
       <c r="H40" s="17">
-        <v>0.0045986753453</v>
+        <v>0.0038760774496</v>
       </c>
       <c r="I40" s="16">
-        <v>6.99</v>
+        <v>6.03</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
@@ -2372,13 +2401,13 @@
         <v>3500000</v>
       </c>
       <c r="G41" s="16">
-        <v>3530.85</v>
+        <v>3597.13</v>
       </c>
       <c r="H41" s="17">
-        <v>0.0040143872178</v>
+        <v>0.0038640999247</v>
       </c>
       <c r="I41" s="16">
-        <v>7.02</v>
+        <v>6.06</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2386,28 +2415,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D42" s="14">
-        <v>7.69</v>
+        <v>7.28</v>
       </c>
       <c r="E42" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="15">
-        <v>3001000</v>
+        <v>3497600</v>
       </c>
       <c r="G42" s="16">
-        <v>3054.56</v>
+        <v>3592.32</v>
       </c>
       <c r="H42" s="17">
-        <v>0.0034728710141</v>
+        <v>0.0038589329386</v>
       </c>
       <c r="I42" s="16">
-        <v>6.97</v>
+        <v>6.05</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2415,28 +2444,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>65</v>
       </c>
       <c r="D43" s="14">
-        <v>7.51</v>
+        <v>7.69</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="15">
-        <v>3000000</v>
+        <v>3001000</v>
       </c>
       <c r="G43" s="16">
-        <v>3037.82</v>
+        <v>3098.60</v>
       </c>
       <c r="H43" s="17">
-        <v>0.0034538385312</v>
+        <v>0.0033285702843</v>
       </c>
       <c r="I43" s="16">
-        <v>7.02</v>
+        <v>6.06</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2444,28 +2473,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>66</v>
       </c>
       <c r="D44" s="14">
-        <v>7.19</v>
+        <v>7.51</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="15">
-        <v>2600000</v>
+        <v>3000000</v>
       </c>
       <c r="G44" s="16">
-        <v>2617.66</v>
+        <v>3084.77</v>
       </c>
       <c r="H44" s="17">
-        <v>0.0029761391292</v>
+        <v>0.0033137138565</v>
       </c>
       <c r="I44" s="16">
-        <v>7.01</v>
+        <v>6.06</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -2473,28 +2502,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>67</v>
       </c>
       <c r="D45" s="14">
-        <v>7.38</v>
+        <v>7.19</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="15">
-        <v>2500000</v>
+        <v>2600000</v>
       </c>
       <c r="G45" s="16">
-        <v>2531.05</v>
+        <v>2663.42</v>
       </c>
       <c r="H45" s="17">
-        <v>0.002877668201</v>
+        <v>0.0028610923212</v>
       </c>
       <c r="I45" s="16">
-        <v>6.97</v>
+        <v>6.05</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2517,13 +2546,13 @@
         <v>2500000</v>
       </c>
       <c r="G46" s="16">
-        <v>2522.11</v>
+        <v>2561.73</v>
       </c>
       <c r="H46" s="17">
-        <v>0.0028675039002</v>
+        <v>0.0027518551456</v>
       </c>
       <c r="I46" s="16">
-        <v>6.99</v>
+        <v>6.08</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2531,28 +2560,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D47" s="14">
-        <v>7.28</v>
+        <v>7.19</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="15">
-        <v>2497600</v>
+        <v>2500000</v>
       </c>
       <c r="G47" s="16">
-        <v>2521.07</v>
+        <v>2560.24</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0028663214759</v>
+        <v>0.0027502545616</v>
       </c>
       <c r="I47" s="16">
-        <v>6.99</v>
+        <v>6.06</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2560,28 +2589,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>72</v>
       </c>
       <c r="D48" s="14">
-        <v>7.19</v>
+        <v>7.23</v>
       </c>
       <c r="E48" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="15">
-        <v>2500000</v>
+        <v>2400000</v>
       </c>
       <c r="G48" s="16">
-        <v>2516.89</v>
+        <v>2458.25</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0028615690399</v>
+        <v>0.0026406951208</v>
       </c>
       <c r="I48" s="16">
-        <v>7.01</v>
+        <v>6.03</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2589,28 +2618,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>73</v>
       </c>
       <c r="D49" s="14">
-        <v>7.03</v>
+        <v>7.41</v>
       </c>
       <c r="E49" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="15">
-        <v>2500000</v>
+        <v>2333000</v>
       </c>
       <c r="G49" s="16">
-        <v>2507.86</v>
+        <v>2405.07</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0028513024139</v>
+        <v>0.0025835682352</v>
       </c>
       <c r="I49" s="16">
-        <v>7.01</v>
+        <v>6.05</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2624,22 +2653,22 @@
         <v>74</v>
       </c>
       <c r="D50" s="14">
-        <v>7.23</v>
+        <v>6.23</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="15">
-        <v>2400000</v>
+        <v>2315800</v>
       </c>
       <c r="G50" s="16">
-        <v>2419.47</v>
+        <v>2329.47</v>
       </c>
       <c r="H50" s="17">
-        <v>0.002750807721</v>
+        <v>0.0025023573937</v>
       </c>
       <c r="I50" s="16">
-        <v>6.97</v>
+        <v>6.04</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2647,28 +2676,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>75</v>
       </c>
       <c r="D51" s="14">
-        <v>7.41</v>
+        <v>8.31</v>
       </c>
       <c r="E51" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="15">
-        <v>2333000</v>
+        <v>2000000</v>
       </c>
       <c r="G51" s="16">
-        <v>2362.50</v>
+        <v>2080.16</v>
       </c>
       <c r="H51" s="17">
-        <v>0.0026860358843</v>
+        <v>0.0022345442337</v>
       </c>
       <c r="I51" s="16">
-        <v>6.99</v>
+        <v>6.07</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2676,28 +2705,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>76</v>
       </c>
       <c r="D52" s="14">
-        <v>6.23</v>
+        <v>7.92</v>
       </c>
       <c r="E52" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="15">
-        <v>2315800</v>
+        <v>2000000</v>
       </c>
       <c r="G52" s="16">
-        <v>2278.55</v>
+        <v>2063.97</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0025905892335</v>
+        <v>0.0022171526527</v>
       </c>
       <c r="I52" s="16">
-        <v>7.02</v>
+        <v>6.09</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -2705,13 +2734,13 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>77</v>
       </c>
       <c r="D53" s="14">
-        <v>8.31</v>
+        <v>7.54</v>
       </c>
       <c r="E53" s="13" t="s">
         <v>18</v>
@@ -2720,13 +2749,13 @@
         <v>2000000</v>
       </c>
       <c r="G53" s="16">
-        <v>2055.42</v>
+        <v>2056.18</v>
       </c>
       <c r="H53" s="17">
-        <v>0.0023369023819</v>
+        <v>0.0022087844985</v>
       </c>
       <c r="I53" s="16">
-        <v>7.03</v>
+        <v>6.10</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
@@ -2734,13 +2763,13 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D54" s="14">
-        <v>7.92</v>
+        <v>7.25</v>
       </c>
       <c r="E54" s="13" t="s">
         <v>18</v>
@@ -2749,13 +2778,13 @@
         <v>2000000</v>
       </c>
       <c r="G54" s="16">
-        <v>2040.38</v>
+        <v>2051.15</v>
       </c>
       <c r="H54" s="17">
-        <v>0.002319802708</v>
+        <v>0.0022033811846</v>
       </c>
       <c r="I54" s="16">
-        <v>6.99</v>
+        <v>6.03</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -2763,13 +2792,13 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>79</v>
       </c>
       <c r="D55" s="14">
-        <v>7.54</v>
+        <v>7.26</v>
       </c>
       <c r="E55" s="13" t="s">
         <v>18</v>
@@ -2778,13 +2807,13 @@
         <v>2000000</v>
       </c>
       <c r="G55" s="16">
-        <v>2027.76</v>
+        <v>2049.72</v>
       </c>
       <c r="H55" s="17">
-        <v>0.0023054544443</v>
+        <v>0.0022018450536</v>
       </c>
       <c r="I55" s="16">
-        <v>6.99</v>
+        <v>6.05</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -2792,13 +2821,13 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D56" s="14">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>18</v>
@@ -2807,13 +2836,13 @@
         <v>2000000</v>
       </c>
       <c r="G56" s="16">
-        <v>2017.31</v>
+        <v>2047.25</v>
       </c>
       <c r="H56" s="17">
-        <v>0.0022935733544</v>
+        <v>0.0021991917364</v>
       </c>
       <c r="I56" s="16">
-        <v>6.97</v>
+        <v>6.10</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -2821,13 +2850,13 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>82</v>
       </c>
       <c r="D57" s="14">
-        <v>7.24</v>
+        <v>7.11</v>
       </c>
       <c r="E57" s="13" t="s">
         <v>18</v>
@@ -2836,13 +2865,13 @@
         <v>2000000</v>
       </c>
       <c r="G57" s="16">
-        <v>2016.46</v>
+        <v>2047.04</v>
       </c>
       <c r="H57" s="17">
-        <v>0.0022926069499</v>
+        <v>0.0021989661507</v>
       </c>
       <c r="I57" s="16">
-        <v>6.98</v>
+        <v>6.06</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -2850,7 +2879,7 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>83</v>
@@ -2865,13 +2894,13 @@
         <v>1822100</v>
       </c>
       <c r="G58" s="16">
-        <v>1838.10</v>
+        <v>1870.97</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0020898211889</v>
+        <v>0.002009828679</v>
       </c>
       <c r="I58" s="16">
-        <v>7.01</v>
+        <v>6.05</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -2879,7 +2908,7 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>84</v>
@@ -2894,13 +2923,13 @@
         <v>1768200</v>
       </c>
       <c r="G59" s="16">
-        <v>1792.79</v>
+        <v>1819.32</v>
       </c>
       <c r="H59" s="17">
-        <v>0.0020383061473</v>
+        <v>0.0019543453461</v>
       </c>
       <c r="I59" s="16">
-        <v>6.97</v>
+        <v>6.04</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -2908,7 +2937,7 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>85</v>
@@ -2923,13 +2952,13 @@
         <v>1500000</v>
       </c>
       <c r="G60" s="16">
-        <v>1519.64</v>
+        <v>1546</v>
       </c>
       <c r="H60" s="17">
-        <v>0.0017277492365</v>
+        <v>0.0016607402244</v>
       </c>
       <c r="I60" s="16">
-        <v>7</v>
+        <v>6.07</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -2952,13 +2981,13 @@
         <v>1500000</v>
       </c>
       <c r="G61" s="16">
-        <v>1510.24</v>
+        <v>1536.04</v>
       </c>
       <c r="H61" s="17">
-        <v>0.0017170619402</v>
+        <v>0.0016500410183</v>
       </c>
       <c r="I61" s="16">
-        <v>7.01</v>
+        <v>6.08</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -2966,7 +2995,7 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>87</v>
@@ -2981,13 +3010,13 @@
         <v>1200000</v>
       </c>
       <c r="G62" s="16">
-        <v>1210.18</v>
+        <v>1229.84</v>
       </c>
       <c r="H62" s="17">
-        <v>0.0013759098016</v>
+        <v>0.0013211156259</v>
       </c>
       <c r="I62" s="16">
-        <v>6.97</v>
+        <v>6.03</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -2995,7 +3024,7 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>88</v>
@@ -3010,13 +3039,13 @@
         <v>1000000</v>
       </c>
       <c r="G63" s="16">
-        <v>1030.92</v>
+        <v>1042.98</v>
       </c>
       <c r="H63" s="17">
-        <v>0.0011721007889</v>
+        <v>0.0011203873475</v>
       </c>
       <c r="I63" s="16">
-        <v>6.99</v>
+        <v>6.11</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -3024,13 +3053,13 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D64" s="14">
-        <v>7.78</v>
+        <v>7.38</v>
       </c>
       <c r="E64" s="13" t="s">
         <v>18</v>
@@ -3039,13 +3068,13 @@
         <v>1000000</v>
       </c>
       <c r="G64" s="16">
-        <v>1017.75</v>
+        <v>1029.86</v>
       </c>
       <c r="H64" s="17">
-        <v>0.0011571272047</v>
+        <v>0.0011062936142</v>
       </c>
       <c r="I64" s="16">
-        <v>6.96</v>
+        <v>6.06</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>13</v>
@@ -3053,13 +3082,13 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D65" s="14">
-        <v>7.11</v>
+        <v>7.78</v>
       </c>
       <c r="E65" s="13" t="s">
         <v>18</v>
@@ -3068,13 +3097,13 @@
         <v>1000000</v>
       </c>
       <c r="G65" s="16">
-        <v>1005.03</v>
+        <v>1029.82</v>
       </c>
       <c r="H65" s="17">
-        <v>0.0011426652464</v>
+        <v>0.0011062506455</v>
       </c>
       <c r="I65" s="16">
-        <v>7.01</v>
+        <v>6.04</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -3082,7 +3111,7 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>91</v>
@@ -3097,13 +3126,13 @@
         <v>815600</v>
       </c>
       <c r="G66" s="16">
-        <v>828.87</v>
+        <v>838.93</v>
       </c>
       <c r="H66" s="17">
-        <v>0.0009423807675</v>
+        <v>0.0009011932707</v>
       </c>
       <c r="I66" s="16">
-        <v>6.99</v>
+        <v>6.06</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>13</v>
@@ -3111,7 +3140,7 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>92</v>
@@ -3126,13 +3155,13 @@
         <v>500000</v>
       </c>
       <c r="G67" s="16">
-        <v>506.96</v>
+        <v>514.12</v>
       </c>
       <c r="H67" s="17">
-        <v>0.00057638635</v>
+        <v>0.0005522766909</v>
       </c>
       <c r="I67" s="16">
-        <v>7</v>
+        <v>6.11</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -3140,7 +3169,7 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>93</v>
@@ -3155,13 +3184,13 @@
         <v>500000</v>
       </c>
       <c r="G68" s="16">
-        <v>504.58</v>
+        <v>513.28</v>
       </c>
       <c r="H68" s="17">
-        <v>0.0005736804175</v>
+        <v>0.0005513743482</v>
       </c>
       <c r="I68" s="16">
-        <v>7.02</v>
+        <v>6.09</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
@@ -3184,13 +3213,13 @@
         <v>500000</v>
       </c>
       <c r="G69" s="16">
-        <v>501.77</v>
+        <v>510.63</v>
       </c>
       <c r="H69" s="17">
-        <v>0.0005704855981</v>
+        <v>0.0005485276719</v>
       </c>
       <c r="I69" s="16">
-        <v>7.01</v>
+        <v>6.06</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -3198,7 +3227,7 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>95</v>
@@ -3213,13 +3242,13 @@
         <v>472500</v>
       </c>
       <c r="G70" s="16">
-        <v>479.86</v>
+        <v>485.91</v>
       </c>
       <c r="H70" s="17">
-        <v>0.0005455751024</v>
+        <v>0.0005219730158</v>
       </c>
       <c r="I70" s="16">
-        <v>6.94</v>
+        <v>6.04</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
@@ -3227,7 +3256,7 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>96</v>
@@ -3242,13 +3271,13 @@
         <v>400000</v>
       </c>
       <c r="G71" s="16">
-        <v>402.77</v>
+        <v>407.73</v>
       </c>
       <c r="H71" s="17">
-        <v>0.0004579279039</v>
+        <v>0.0004379906932</v>
       </c>
       <c r="I71" s="16">
-        <v>6.94</v>
+        <v>6.03</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -3256,7 +3285,7 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>97</v>
@@ -3271,13 +3300,13 @@
         <v>333000</v>
       </c>
       <c r="G72" s="16">
-        <v>345.21</v>
+        <v>349.83</v>
       </c>
       <c r="H72" s="17">
-        <v>0.0003924852688</v>
+        <v>0.0003757935011</v>
       </c>
       <c r="I72" s="16">
-        <v>7.02</v>
+        <v>6.11</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
@@ -3285,7 +3314,7 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C73" s="13" t="s">
         <v>98</v>
@@ -3300,13 +3329,13 @@
         <v>300000</v>
       </c>
       <c r="G73" s="16">
-        <v>306.07</v>
+        <v>309.47</v>
       </c>
       <c r="H73" s="17">
-        <v>0.0003479851865</v>
+        <v>0.0003324380836</v>
       </c>
       <c r="I73" s="16">
-        <v>6.98</v>
+        <v>6.10</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
@@ -3337,10 +3366,10 @@
         <v>13</v>
       </c>
       <c r="G75" s="9">
-        <v>335287.52999999997</v>
+        <v>356488.23</v>
       </c>
       <c r="H75" s="10">
-        <v>0.38120395223040004</v>
+        <v>0.3829458881691999</v>
       </c>
       <c r="I75" s="9" t="s">
         <v>13</v>
@@ -3357,22 +3386,22 @@
         <v>101</v>
       </c>
       <c r="D76" s="14">
-        <v>7.33</v>
+        <v>7.70</v>
       </c>
       <c r="E76" s="13" t="s">
         <v>102</v>
       </c>
       <c r="F76" s="15">
-        <v>4700</v>
+        <v>53000</v>
       </c>
       <c r="G76" s="16">
-        <v>46993.28</v>
+        <v>54206.70</v>
       </c>
       <c r="H76" s="17">
-        <v>0.0534288408051</v>
+        <v>0.0582297846868</v>
       </c>
       <c r="I76" s="16">
-        <v>7.34</v>
+        <v>6.59</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3386,22 +3415,22 @@
         <v>104</v>
       </c>
       <c r="D77" s="14">
-        <v>7.70</v>
+        <v>7.33</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>105</v>
       </c>
       <c r="F77" s="15">
-        <v>42500</v>
+        <v>4950</v>
       </c>
       <c r="G77" s="16">
-        <v>42651.94</v>
+        <v>50336.25</v>
       </c>
       <c r="H77" s="17">
-        <v>0.0484929698946</v>
+        <v>0.0540720796404</v>
       </c>
       <c r="I77" s="16">
-        <v>7.52</v>
+        <v>6.51</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
@@ -3409,28 +3438,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D78" s="14">
-        <v>7.80</v>
+        <v>7.75</v>
       </c>
       <c r="E78" s="13" t="s">
         <v>105</v>
       </c>
       <c r="F78" s="15">
-        <v>29000</v>
+        <v>2900</v>
       </c>
       <c r="G78" s="16">
-        <v>29131.72</v>
+        <v>29646.58</v>
       </c>
       <c r="H78" s="17">
-        <v>0.0331212043564</v>
+        <v>0.0318468744657</v>
       </c>
       <c r="I78" s="16">
-        <v>7.54</v>
+        <v>6.52</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>13</v>
@@ -3438,28 +3467,28 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D79" s="14">
-        <v>7.75</v>
+        <v>6.57</v>
       </c>
       <c r="E79" s="13" t="s">
         <v>102</v>
       </c>
       <c r="F79" s="15">
-        <v>2850</v>
+        <v>2900</v>
       </c>
       <c r="G79" s="16">
-        <v>28698.84</v>
+        <v>28992.11</v>
       </c>
       <c r="H79" s="17">
-        <v>0.0326290429962</v>
+        <v>0.0311438313514</v>
       </c>
       <c r="I79" s="16">
-        <v>7.52</v>
+        <v>6.59</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>13</v>
@@ -3467,28 +3496,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C80" s="13" t="s">
         <v>110</v>
       </c>
       <c r="D80" s="14">
-        <v>6.57</v>
+        <v>7.44</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>105</v>
       </c>
       <c r="F80" s="15">
-        <v>2900</v>
+        <v>2745</v>
       </c>
       <c r="G80" s="16">
-        <v>28409.59</v>
+        <v>27915.47</v>
       </c>
       <c r="H80" s="17">
-        <v>0.0323001812482</v>
+        <v>0.0299872858434</v>
       </c>
       <c r="I80" s="16">
-        <v>7.53</v>
+        <v>6.52</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>13</v>
@@ -3496,28 +3525,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C81" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C81" s="13" t="s">
-        <v>112</v>
-      </c>
       <c r="D81" s="14">
-        <v>7.20</v>
+        <v>7.80</v>
       </c>
       <c r="E81" s="13" t="s">
         <v>102</v>
       </c>
       <c r="F81" s="15">
-        <v>2570</v>
+        <v>26500</v>
       </c>
       <c r="G81" s="16">
-        <v>25612.18</v>
+        <v>27020.75</v>
       </c>
       <c r="H81" s="17">
-        <v>0.0291196760024</v>
+        <v>0.0290261619795</v>
       </c>
       <c r="I81" s="16">
-        <v>7.33</v>
+        <v>6.57</v>
       </c>
       <c r="J81" s="11" t="s">
         <v>13</v>
@@ -3525,28 +3554,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>113</v>
       </c>
       <c r="D82" s="14">
-        <v>7.44</v>
+        <v>7.20</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F82" s="15">
-        <v>2495</v>
+        <v>2620</v>
       </c>
       <c r="G82" s="16">
-        <v>24900.80</v>
+        <v>26603.30</v>
       </c>
       <c r="H82" s="17">
-        <v>0.0283108750681</v>
+        <v>0.0285777298924</v>
       </c>
       <c r="I82" s="16">
-        <v>7.51</v>
+        <v>6.41</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>13</v>
@@ -3563,19 +3592,19 @@
         <v>7.22</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F83" s="15">
-        <v>2250</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="16">
-        <v>22421.34</v>
+        <v>20300</v>
       </c>
       <c r="H83" s="17">
-        <v>0.0254918619321</v>
+        <v>0.0218066148491</v>
       </c>
       <c r="I83" s="16">
-        <v>7.35</v>
+        <v>6.44</v>
       </c>
       <c r="J83" s="11" t="s">
         <v>13</v>
@@ -3583,7 +3612,7 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>116</v>
@@ -3592,19 +3621,19 @@
         <v>6.35</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F84" s="15">
         <v>5250</v>
       </c>
       <c r="G84" s="16">
-        <v>15353.57</v>
+        <v>15698.09</v>
       </c>
       <c r="H84" s="17">
-        <v>0.0174561862317</v>
+        <v>0.0168631626845</v>
       </c>
       <c r="I84" s="16">
-        <v>7.51</v>
+        <v>6.52</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>13</v>
@@ -3612,28 +3641,28 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C85" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="C85" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="D85" s="14">
         <v>7.27</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F85" s="15">
         <v>1350</v>
       </c>
       <c r="G85" s="16">
-        <v>13475.74</v>
+        <v>13694.24</v>
       </c>
       <c r="H85" s="17">
-        <v>0.015321194162</v>
+        <v>0.0147105919867</v>
       </c>
       <c r="I85" s="16">
-        <v>7.35</v>
+        <v>6.50</v>
       </c>
       <c r="J85" s="11" t="s">
         <v>13</v>
@@ -3641,28 +3670,28 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D86" s="14">
         <v>7.49</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F86" s="15">
-        <v>1210</v>
+        <v>1260</v>
       </c>
       <c r="G86" s="16">
-        <v>12132.57</v>
+        <v>12826.49</v>
       </c>
       <c r="H86" s="17">
-        <v>0.0137940818578</v>
+        <v>0.0137784397682</v>
       </c>
       <c r="I86" s="16">
-        <v>7.35</v>
+        <v>6.50</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>13</v>
@@ -3670,28 +3699,28 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D87" s="14">
         <v>7.15</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F87" s="15">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="G87" s="16">
-        <v>8269.08</v>
+        <v>8240.33</v>
       </c>
       <c r="H87" s="17">
-        <v>0.0094015007874</v>
+        <v>0.008851906529</v>
       </c>
       <c r="I87" s="16">
-        <v>7.50</v>
+        <v>6.53</v>
       </c>
       <c r="J87" s="11" t="s">
         <v>13</v>
@@ -3699,28 +3728,28 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C88" s="13" t="s">
         <v>121</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>122</v>
       </c>
       <c r="D88" s="14">
         <v>7.52</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F88" s="15">
         <v>650</v>
       </c>
       <c r="G88" s="16">
-        <v>6528.65</v>
+        <v>6638.83</v>
       </c>
       <c r="H88" s="17">
-        <v>0.0074227251539</v>
+        <v>0.0071315472344</v>
       </c>
       <c r="I88" s="16">
-        <v>7.28</v>
+        <v>6.36</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>13</v>
@@ -3731,25 +3760,25 @@
         <v>114</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D89" s="14">
         <v>7.56</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F89" s="15">
         <v>650</v>
       </c>
       <c r="G89" s="16">
-        <v>6523.02</v>
+        <v>6630.68</v>
       </c>
       <c r="H89" s="17">
-        <v>0.0074163241456</v>
+        <v>0.0071227923619</v>
       </c>
       <c r="I89" s="16">
-        <v>7.36</v>
+        <v>6.43</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>13</v>
@@ -3757,28 +3786,28 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D90" s="14">
         <v>7.30</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F90" s="15">
         <v>550</v>
       </c>
       <c r="G90" s="16">
-        <v>5472.65</v>
+        <v>5582.12</v>
       </c>
       <c r="H90" s="17">
-        <v>0.0062221097491</v>
+        <v>0.0059964108808</v>
       </c>
       <c r="I90" s="16">
-        <v>7.50</v>
+        <v>6.53</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
@@ -3786,28 +3815,28 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D91" s="14">
         <v>8.50</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F91" s="15">
         <v>4500</v>
       </c>
       <c r="G91" s="16">
-        <v>4616.82</v>
+        <v>4683.69</v>
       </c>
       <c r="H91" s="17">
-        <v>0.0052490769064</v>
+        <v>0.00503130167</v>
       </c>
       <c r="I91" s="16">
-        <v>7.27</v>
+        <v>6.37</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
@@ -3815,28 +3844,28 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D92" s="14">
         <v>10.040000000000001</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F92" s="15">
         <v>300</v>
       </c>
       <c r="G92" s="16">
-        <v>3179.79</v>
+        <v>3203.97</v>
       </c>
       <c r="H92" s="17">
-        <v>0.0036152508125</v>
+        <v>0.0034417605802</v>
       </c>
       <c r="I92" s="16">
-        <v>7.35</v>
+        <v>6.50</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>13</v>
@@ -3844,28 +3873,28 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D93" s="14">
-        <v>7.23</v>
+        <v>9.25</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F93" s="15">
         <v>250</v>
       </c>
       <c r="G93" s="16">
-        <v>2487.45</v>
+        <v>2614.64</v>
       </c>
       <c r="H93" s="17">
-        <v>0.0028280973377</v>
+        <v>0.0028086919925</v>
       </c>
       <c r="I93" s="16">
-        <v>7.52</v>
+        <v>6.40</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>13</v>
@@ -3873,28 +3902,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D94" s="14">
-        <v>7.95</v>
+        <v>9.3</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F94" s="15">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G94" s="16">
-        <v>1693.64</v>
+        <v>2109.14</v>
       </c>
       <c r="H94" s="17">
-        <v>0.0019255779111</v>
+        <v>0.0022656750563</v>
       </c>
       <c r="I94" s="16">
-        <v>7.51</v>
+        <v>6.40</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
@@ -3902,28 +3931,28 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D95" s="14">
-        <v>7.10</v>
+        <v>7.890000000000001</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F95" s="15">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="G95" s="16">
-        <v>1611.72</v>
+        <v>2047.66</v>
       </c>
       <c r="H95" s="17">
-        <v>0.0018324392615</v>
+        <v>0.0021996321656</v>
       </c>
       <c r="I95" s="16">
-        <v>7.52</v>
+        <v>6.40</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
@@ -3931,28 +3960,28 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D96" s="14">
-        <v>9.35</v>
+        <v>7.95</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F96" s="15">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="G96" s="16">
-        <v>1045.16</v>
+        <v>1718.72</v>
       </c>
       <c r="H96" s="17">
-        <v>0.0011882909057</v>
+        <v>0.0018462790676</v>
       </c>
       <c r="I96" s="16">
-        <v>7.33</v>
+        <v>6.52</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>13</v>
@@ -3960,28 +3989,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="12" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D97" s="14">
-        <v>9.3</v>
+        <v>7.10</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F97" s="15">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="G97" s="16">
-        <v>1041.11</v>
+        <v>1636.62</v>
       </c>
       <c r="H97" s="17">
-        <v>0.0011836862728</v>
+        <v>0.0017580858125</v>
       </c>
       <c r="I97" s="16">
-        <v>7.34</v>
+        <v>6.52</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
@@ -3989,28 +4018,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D98" s="14">
-        <v>8.40</v>
+        <v>9.35</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F98" s="15">
         <v>100</v>
       </c>
       <c r="G98" s="16">
-        <v>1021.30</v>
+        <v>1059.22</v>
       </c>
       <c r="H98" s="17">
-        <v>0.0011611633645</v>
+        <v>0.0011378326394</v>
       </c>
       <c r="I98" s="16">
-        <v>7.34</v>
+        <v>6.41</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
@@ -4018,28 +4047,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D99" s="14">
-        <v>7.930000000000001</v>
+        <v>8.40</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F99" s="15">
         <v>100</v>
       </c>
       <c r="G99" s="16">
-        <v>1011.58</v>
+        <v>1036.26</v>
       </c>
       <c r="H99" s="17">
-        <v>0.0011501122454</v>
+        <v>0.001113168606</v>
       </c>
       <c r="I99" s="16">
-        <v>7.34</v>
+        <v>6.40</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
@@ -4047,28 +4076,28 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D100" s="14">
-        <v>7.60</v>
+        <v>7.930000000000001</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F100" s="15">
         <v>100</v>
       </c>
       <c r="G100" s="16">
-        <v>1003.99</v>
+        <v>1027.45</v>
       </c>
       <c r="H100" s="17">
-        <v>0.0011414828222</v>
+        <v>0.00110370475</v>
       </c>
       <c r="I100" s="16">
-        <v>7.52</v>
+        <v>6.40</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
@@ -4076,43 +4105,64 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>13</v>
+        <v>106</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D101" s="14">
+        <v>7.60</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F101" s="15">
+        <v>100</v>
+      </c>
+      <c r="G101" s="16">
+        <v>1018.92</v>
+      </c>
+      <c r="H101" s="17">
+        <v>0.0010945416749</v>
+      </c>
+      <c r="I101" s="16">
+        <v>6.52</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="15" customHeight="1">
+      <c r="B103" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G102" s="9" t="s">
+      <c r="C103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H102" s="10" t="s">
+      <c r="H103" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="12" t="s">
+      <c r="I103" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J103" s="11" t="s">
@@ -4120,36 +4170,36 @@
       </c>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" ht="15" customHeight="1">
+      <c r="B105" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="9" t="s">
+      <c r="C105" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H104" s="10" t="s">
+      <c r="H105" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J104" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="12" t="s">
+      <c r="I105" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J105" s="11" t="s">
@@ -4157,36 +4207,36 @@
       </c>
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J106" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" ht="15" customHeight="1">
+      <c r="B107" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="9" t="s">
+      <c r="C107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H106" s="10" t="s">
+      <c r="H107" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J106" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" ht="15" customHeight="1">
-      <c r="B107" s="12" t="s">
+      <c r="I107" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J107" s="11" t="s">
@@ -4194,36 +4244,36 @@
       </c>
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J108" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" ht="15" customHeight="1">
+      <c r="B109" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="9" t="s">
+      <c r="C109" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H108" s="10" t="s">
+      <c r="H109" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J108" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="2:10" ht="15" customHeight="1">
-      <c r="B109" s="12" t="s">
+      <c r="I109" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J109" s="11" t="s">
@@ -4231,36 +4281,36 @@
       </c>
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J110" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" ht="15" customHeight="1">
+      <c r="B111" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" s="9" t="s">
+      <c r="C111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H110" s="10" t="s">
+      <c r="H111" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I110" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J110" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="2:10" ht="15" customHeight="1">
-      <c r="B111" s="12" t="s">
+      <c r="I111" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J111" s="11" t="s">
@@ -4268,36 +4318,36 @@
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J112" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" ht="15" customHeight="1">
+      <c r="B113" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="9" t="s">
+      <c r="C113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H112" s="10" t="s">
+      <c r="H113" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J112" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="113" spans="2:10" ht="15" customHeight="1">
-      <c r="B113" s="12" t="s">
+      <c r="I113" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
@@ -4305,36 +4355,36 @@
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J114" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10" ht="15" customHeight="1">
+      <c r="B115" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="9" t="s">
+      <c r="C115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H114" s="10" t="s">
+      <c r="H115" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J114" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="2:10" ht="15" customHeight="1">
-      <c r="B115" s="12" t="s">
+      <c r="I115" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J115" s="11" t="s">
@@ -4342,36 +4392,36 @@
       </c>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10" ht="15" customHeight="1">
+      <c r="B117" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="9" t="s">
+      <c r="C117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H116" s="10" t="s">
+      <c r="H117" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I116" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J116" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="12" t="s">
+      <c r="I117" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J117" s="11" t="s">
@@ -4379,36 +4429,36 @@
       </c>
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10" ht="15" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C118" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="9" t="s">
+      <c r="C119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H118" s="10" t="s">
+      <c r="H119" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I118" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J118" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="119" spans="2:10" ht="15" customHeight="1">
-      <c r="B119" s="12" t="s">
+      <c r="I119" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J119" s="11" t="s">
@@ -4416,36 +4466,36 @@
       </c>
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
-      <c r="B120" s="7" t="s">
+      <c r="B120" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10" ht="15" customHeight="1">
+      <c r="B121" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C120" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F120" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="9" t="s">
+      <c r="C121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H120" s="10" t="s">
+      <c r="H121" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I120" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J120" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="121" spans="2:10" ht="15" customHeight="1">
-      <c r="B121" s="12" t="s">
+      <c r="I121" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J121" s="11" t="s">
@@ -4453,36 +4503,36 @@
       </c>
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J122" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" ht="15" customHeight="1">
+      <c r="B123" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F122" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="9" t="s">
+      <c r="C123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H122" s="10" t="s">
+      <c r="H123" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I122" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J122" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="2:10" ht="15" customHeight="1">
-      <c r="B123" s="12" t="s">
+      <c r="I123" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J123" s="11" t="s">
@@ -4490,36 +4540,36 @@
       </c>
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
-      <c r="B124" s="7" t="s">
+      <c r="B124" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" ht="15" customHeight="1">
+      <c r="B125" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G124" s="9" t="s">
+      <c r="C125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H124" s="10" t="s">
+      <c r="H125" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I124" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="125" spans="2:10" ht="15" customHeight="1">
-      <c r="B125" s="12" t="s">
+      <c r="I125" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J125" s="11" t="s">
@@ -4527,36 +4577,36 @@
       </c>
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
-      <c r="B126" s="7" t="s">
+      <c r="B126" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J126" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" ht="15" customHeight="1">
+      <c r="B127" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C126" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F126" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="9">
-        <v>5896.96</v>
-      </c>
-      <c r="H126" s="10">
-        <v>0.0067045274787</v>
-      </c>
-      <c r="I126" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J126" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="12" t="s">
+      <c r="C127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="9">
+        <v>7847.09</v>
+      </c>
+      <c r="H127" s="10">
+        <v>0.0084294812471</v>
+      </c>
+      <c r="I127" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J127" s="11" t="s">
@@ -4564,78 +4614,74 @@
       </c>
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
-      <c r="B128" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C128" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D128" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E128" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F128" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G128" s="19">
-        <v>25569.97446668998</v>
-      </c>
-      <c r="H128" s="20">
-        <v>0.02907169057307107</v>
-      </c>
-      <c r="I128" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J128" s="21" t="s">
+      <c r="B128" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J128" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1">
       <c r="B129" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="19">
+        <v>24201.64126235014</v>
+      </c>
+      <c r="H129" s="20">
+        <v>0.025997826094837122</v>
+      </c>
+      <c r="I129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" ht="15" customHeight="1">
+      <c r="B130" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C129" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D129" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G129" s="19">
-        <v>879548.93446669</v>
-      </c>
-      <c r="H129" s="20">
-        <v>0.9999999999956709</v>
-      </c>
-      <c r="I129" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J129" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="132" spans="2:9" ht="15" customHeight="1">
-      <c r="B132" s="13" t="s">
+      <c r="C130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="19">
+        <v>930910.19126235</v>
+      </c>
+      <c r="H130" s="20">
+        <v>0.9999999999956367</v>
+      </c>
+      <c r="I130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9" ht="15" customHeight="1">
+      <c r="B133" s="13" t="s">
         <v>153</v>
-      </c>
-      <c r="C132" s="22"/>
-      <c r="D132" s="22"/>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
-      <c r="G132" s="22"/>
-      <c r="H132" s="22"/>
-      <c r="I132" s="22"/>
-    </row>
-    <row r="133" spans="2:8" ht="15" customHeight="1">
-      <c r="B133" s="13" t="s">
-        <v>154</v>
       </c>
       <c r="C133" s="22"/>
       <c r="D133" s="22"/>
@@ -4643,10 +4689,11 @@
       <c r="F133" s="22"/>
       <c r="G133" s="22"/>
       <c r="H133" s="22"/>
+      <c r="I133" s="22"/>
     </row>
     <row r="134" spans="2:8" ht="15" customHeight="1">
       <c r="B134" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C134" s="22"/>
       <c r="D134" s="22"/>
@@ -4655,9 +4702,9 @@
       <c r="G134" s="22"/>
       <c r="H134" s="22"/>
     </row>
-    <row r="135" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B135" s="23" t="s">
-        <v>156</v>
+    <row r="135" spans="2:8" ht="15" customHeight="1">
+      <c r="B135" s="13" t="s">
+        <v>155</v>
       </c>
       <c r="C135" s="22"/>
       <c r="D135" s="22"/>
@@ -4668,7 +4715,7 @@
     </row>
     <row r="136" spans="2:8" ht="27.6" customHeight="1">
       <c r="B136" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C136" s="22"/>
       <c r="D136" s="22"/>
@@ -4679,7 +4726,7 @@
     </row>
     <row r="137" spans="2:8" ht="27.6" customHeight="1">
       <c r="B137" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C137" s="22"/>
       <c r="D137" s="22"/>
@@ -4688,32 +4735,61 @@
       <c r="G137" s="22"/>
       <c r="H137" s="22"/>
     </row>
-    <row r="140" ht="15">
-      <c r="B140" s="22" t="s">
+    <row r="138" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B138" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C138" s="22"/>
+      <c r="D138" s="22"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
+      <c r="H138" s="22"/>
+    </row>
+    <row r="139" spans="2:6" ht="15" customHeight="1">
+      <c r="B139" s="24" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="155" ht="15">
-      <c r="B155" s="22" t="s">
+      <c r="C139" s="25">
+        <v>0.8307625777982011</v>
+      </c>
+      <c r="D139" s="26"/>
+      <c r="E139" s="27"/>
+      <c r="F139" s="27"/>
+    </row>
+    <row r="140" spans="2:8" ht="30.75" customHeight="1">
+      <c r="B140" s="28" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="156" ht="15">
-      <c r="B156" s="22" t="s">
+      <c r="C140" s="29"/>
+      <c r="D140" s="29"/>
+      <c r="E140" s="29"/>
+      <c r="F140" s="29"/>
+      <c r="G140" s="29"/>
+      <c r="H140" s="29"/>
+    </row>
+    <row r="143" ht="15">
+      <c r="B143" s="22" t="s">
         <v>161</v>
       </c>
     </row>
+    <row r="158" ht="15">
+      <c r="B158" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B133:I133"/>
     <mergeCell ref="B134:H134"/>
+    <mergeCell ref="B140:H140"/>
     <mergeCell ref="B135:H135"/>
     <mergeCell ref="B136:H136"/>
     <mergeCell ref="B137:H137"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B132:I132"/>
-    <mergeCell ref="B133:H133"/>
+    <mergeCell ref="B138:H138"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
